--- a/main/ig/FRSectionUncodedPointsOfVigilanceLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionUncodedPointsOfVigilanceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionUncodedPointsOfVigilanceLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionUncodedPointsOfVigilanceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionUncodedPointsOfVigilanceLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionUncodedPointsOfVigilanceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
